--- a/data/trans_orig/IP07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2007 (tasa de respuesta: 99,81%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2007 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28493</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44955</t>
+          <t>45160</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>31104</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49476</t>
+          <t>48984</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65286</t>
+          <t>64740</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88814</t>
+          <t>88471</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53653</t>
+          <t>53863</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72189</t>
+          <t>72434</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56770</t>
+          <t>57737</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77420</t>
+          <t>78102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115428</t>
+          <t>117244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142930</t>
+          <t>144480</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28830</t>
+          <t>28074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44848</t>
+          <t>44267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32574</t>
+          <t>32540</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>50047</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65336</t>
+          <t>65290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>89235</t>
+          <t>89395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>17174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21439</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39148</t>
+          <t>39430</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>57154</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35747</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55325</t>
+          <t>55125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>80158</t>
+          <t>80091</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>107688</t>
+          <t>107777</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78613</t>
+          <t>78214</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100228</t>
+          <t>98993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82129</t>
+          <t>81664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105688</t>
+          <t>103885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164103</t>
+          <t>165167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198732</t>
+          <t>197255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44250</t>
+          <t>44493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62929</t>
+          <t>63880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50009</t>
+          <t>50165</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70864</t>
+          <t>72095</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99369</t>
+          <t>101621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129034</t>
+          <t>130288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32774</t>
+          <t>33424</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29372</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>38480</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57749</t>
+          <t>57479</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57919</t>
+          <t>58870</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76285</t>
+          <t>76882</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76250</t>
+          <t>75858</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94424</t>
+          <t>94950</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141509</t>
+          <t>139706</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>167792</t>
+          <t>165853</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34935</t>
+          <t>35324</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50688</t>
+          <t>51411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>30874</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46730</t>
+          <t>47344</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69201</t>
+          <t>69995</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92874</t>
+          <t>93706</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11146</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>23181</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40599</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27805</t>
+          <t>26918</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45583</t>
+          <t>44688</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>55452</t>
+          <t>54757</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>79752</t>
+          <t>80670</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92581</t>
+          <t>93707</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116516</t>
+          <t>116780</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85708</t>
+          <t>85805</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108715</t>
+          <t>109052</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>184070</t>
+          <t>186820</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>217499</t>
+          <t>218335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,42%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60780</t>
+          <t>59807</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83373</t>
+          <t>82687</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58707</t>
+          <t>57772</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>81115</t>
+          <t>80455</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>124603</t>
+          <t>125589</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>156105</t>
+          <t>156432</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29609</t>
+          <t>29637</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>23169</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41204</t>
+          <t>40724</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>124187</t>
+          <t>124240</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>157613</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>126943</t>
+          <t>125719</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>160553</t>
+          <t>160224</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>259826</t>
+          <t>259266</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>309685</t>
+          <t>307498</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>303473</t>
+          <t>307527</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>344318</t>
+          <t>347175</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>323699</t>
+          <t>322165</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>363392</t>
+          <t>364878</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>638179</t>
+          <t>637028</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>701740</t>
+          <t>698474</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>184527</t>
+          <t>185137</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>221686</t>
+          <t>223318</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>188960</t>
+          <t>189871</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>227575</t>
+          <t>229456</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>383793</t>
+          <t>386189</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>439661</t>
+          <t>440997</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34935</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>23901</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41832</t>
+          <t>40743</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47223</t>
+          <t>47743</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69433</t>
+          <t>69960</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48852</t>
+          <t>48881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67917</t>
+          <t>68541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56968</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77927</t>
+          <t>77808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111503</t>
+          <t>113080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139904</t>
+          <t>140598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40819</t>
+          <t>41398</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59683</t>
+          <t>60063</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43530</t>
+          <t>43261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63896</t>
+          <t>63225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88489</t>
+          <t>87292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115637</t>
+          <t>115824</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,49 +5185,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7221</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>3,25%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>6878</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48128</t>
+          <t>48491</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69199</t>
+          <t>68749</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50563</t>
+          <t>49879</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72980</t>
+          <t>71389</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>102572</t>
+          <t>104005</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131378</t>
+          <t>133485</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89224</t>
+          <t>88804</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111176</t>
+          <t>111462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104919</t>
+          <t>103905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129346</t>
+          <t>129072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>202485</t>
+          <t>202527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232852</t>
+          <t>234549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36469</t>
+          <t>36812</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54592</t>
+          <t>54544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32816</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51865</t>
+          <t>52135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75325</t>
+          <t>75161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102114</t>
+          <t>101694</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23091</t>
+          <t>23077</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39327</t>
+          <t>39701</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>20649</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36876</t>
+          <t>36006</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48075</t>
+          <t>47898</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71314</t>
+          <t>69769</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>70974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90709</t>
+          <t>89893</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80384</t>
+          <t>80888</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100862</t>
+          <t>101074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>156630</t>
+          <t>157751</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184914</t>
+          <t>186658</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>30025</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46284</t>
+          <t>47612</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33491</t>
+          <t>33381</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50603</t>
+          <t>50955</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68234</t>
+          <t>67490</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>94137</t>
+          <t>92351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15565</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35819</t>
+          <t>34482</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54824</t>
+          <t>53732</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>40936</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61714</t>
+          <t>60603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81759</t>
+          <t>80530</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>111911</t>
+          <t>110787</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100449</t>
+          <t>101534</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124897</t>
+          <t>124445</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>83518</t>
+          <t>84344</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108125</t>
+          <t>109036</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>191125</t>
+          <t>192980</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>226911</t>
+          <t>226680</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36523</t>
+          <t>36998</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57118</t>
+          <t>57343</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42354</t>
+          <t>42896</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>63669</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>86665</t>
+          <t>84632</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116241</t>
+          <t>114632</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9884</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22463</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>41103</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>142190</t>
+          <t>141628</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>177439</t>
+          <t>177477</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>152068</t>
+          <t>151536</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>190399</t>
+          <t>190205</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>305014</t>
+          <t>303781</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>356232</t>
+          <t>354970</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>332218</t>
+          <t>332494</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>375280</t>
+          <t>376184</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>348496</t>
+          <t>347373</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>393479</t>
+          <t>394203</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>692281</t>
+          <t>692393</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>756128</t>
+          <t>753110</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,62%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>161351</t>
+          <t>160800</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>199092</t>
+          <t>199070</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>170573</t>
+          <t>170322</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>210301</t>
+          <t>209592</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>341915</t>
+          <t>345202</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>397047</t>
+          <t>398560</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2016 (tasa de respuesta: 99,48%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2016 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13573</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30531</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26525</t>
+          <t>26191</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45638</t>
+          <t>44894</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>34200</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53509</t>
+          <t>52831</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>39025</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>58744</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78243</t>
+          <t>78761</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104351</t>
+          <t>105311</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63581</t>
+          <t>63194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82732</t>
+          <t>83218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63301</t>
+          <t>63708</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84218</t>
+          <t>84308</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132752</t>
+          <t>131866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>160905</t>
+          <t>160655</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>789</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32343</t>
+          <t>32276</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20194</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36890</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42909</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64183</t>
+          <t>63994</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>76504</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99522</t>
+          <t>98310</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78583</t>
+          <t>78696</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101859</t>
+          <t>102579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162105</t>
+          <t>160868</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191854</t>
+          <t>194652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79432</t>
+          <t>79275</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102127</t>
+          <t>100379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88116</t>
+          <t>89197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112343</t>
+          <t>113773</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175385</t>
+          <t>174498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>207334</t>
+          <t>206593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,15%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27688</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27557</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45745</t>
+          <t>44672</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41840</t>
+          <t>43053</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59776</t>
+          <t>60923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43759</t>
+          <t>44265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64426</t>
+          <t>63100</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91546</t>
+          <t>91910</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118659</t>
+          <t>119743</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75191</t>
+          <t>75356</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94125</t>
+          <t>93616</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77232</t>
+          <t>76915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98983</t>
+          <t>97865</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>157862</t>
+          <t>157876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>186179</t>
+          <t>186156</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>812</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33072</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27853</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32658</t>
+          <t>32302</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55041</t>
+          <t>54038</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>69567</t>
+          <t>69492</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93714</t>
+          <t>94607</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70501</t>
+          <t>70504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93557</t>
+          <t>93929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147896</t>
+          <t>147025</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>180893</t>
+          <t>180516</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,91%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87387</t>
+          <t>86639</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110971</t>
+          <t>110366</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>90131</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>113238</t>
+          <t>112736</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>183979</t>
+          <t>183902</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>218044</t>
+          <t>217610</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35510</t>
+          <t>35043</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63457</t>
+          <t>63945</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89609</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>74469</t>
+          <t>74828</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>103999</t>
+          <t>104898</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>145624</t>
+          <t>146596</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>183776</t>
+          <t>185168</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>243966</t>
+          <t>243401</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>284085</t>
+          <t>283171</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>252359</t>
+          <t>253269</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>293813</t>
+          <t>295461</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>508615</t>
+          <t>507798</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>570362</t>
+          <t>566974</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>324372</t>
+          <t>327234</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>367000</t>
+          <t>367850</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>342881</t>
+          <t>339023</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>385964</t>
+          <t>383060</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>678899</t>
+          <t>678694</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>741576</t>
+          <t>741288</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general percibida por adulto en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según su salud general percibida por el adulto en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30502</t>
+          <t>29460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64967</t>
+          <t>64817</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52951</t>
+          <t>53629</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>93622</t>
+          <t>96011</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43410</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60485</t>
+          <t>61867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42706</t>
+          <t>45393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72807</t>
+          <t>75870</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95936</t>
+          <t>94406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128897</t>
+          <t>128717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29054</t>
+          <t>28225</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45789</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23033</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44329</t>
+          <t>44610</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56785</t>
+          <t>55348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85200</t>
+          <t>84297</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34167</t>
+          <t>31923</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39898</t>
+          <t>40814</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29640</t>
+          <t>29511</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48352</t>
+          <t>47691</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46007</t>
+          <t>45829</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69750</t>
+          <t>70754</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79822</t>
+          <t>82629</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110598</t>
+          <t>113966</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68709</t>
+          <t>68600</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93470</t>
+          <t>92956</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93227</t>
+          <t>94399</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123004</t>
+          <t>123252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>172460</t>
+          <t>169316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210356</t>
+          <t>209397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48510</t>
+          <t>49684</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70783</t>
+          <t>71688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69326</t>
+          <t>70091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100400</t>
+          <t>99980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125866</t>
+          <t>126304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161810</t>
+          <t>163594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,77 +13151,77 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>7766</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6267</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>12242</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2733</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>7688</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6267</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>2854</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>12239</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37516</t>
+          <t>37196</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27609</t>
+          <t>27501</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50212</t>
+          <t>51021</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49276</t>
+          <t>48260</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81712</t>
+          <t>80920</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41007</t>
+          <t>40630</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83892</t>
+          <t>85086</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70358</t>
+          <t>72477</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99267</t>
+          <t>99385</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115231</t>
+          <t>114228</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174269</t>
+          <t>174544</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70654</t>
+          <t>69389</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>131305</t>
+          <t>130335</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48504</t>
+          <t>48392</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73908</t>
+          <t>72546</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125679</t>
+          <t>126457</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>203076</t>
+          <t>208852</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29770</t>
+          <t>31341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48541</t>
+          <t>49304</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19886</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36576</t>
+          <t>36704</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>54764</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>79808</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61093</t>
+          <t>60425</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>82232</t>
+          <t>82200</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70332</t>
+          <t>71491</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94601</t>
+          <t>94305</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136703</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>168545</t>
+          <t>169474</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,53%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43684</t>
+          <t>44561</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>65421</t>
+          <t>66972</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53717</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>77577</t>
+          <t>76480</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105150</t>
+          <t>104666</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>136932</t>
+          <t>136271</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42397</t>
+          <t>43706</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28009</t>
+          <t>27555</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>27346</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62267</t>
+          <t>61701</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>110284</t>
+          <t>109651</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>146851</t>
+          <t>146244</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>142360</t>
+          <t>141959</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>200330</t>
+          <t>195018</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>262206</t>
+          <t>265765</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>328439</t>
+          <t>330636</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>238111</t>
+          <t>234971</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>298724</t>
+          <t>296518</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>309217</t>
+          <t>308951</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>367424</t>
+          <t>365508</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>561897</t>
+          <t>565373</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>644838</t>
+          <t>648112</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,38%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>216159</t>
+          <t>214810</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>300801</t>
+          <t>299724</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>216796</t>
+          <t>216137</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>270262</t>
+          <t>268832</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>446023</t>
+          <t>447564</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>545985</t>
+          <t>545543</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
